--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487725_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487725_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2664</v>
+        <v>4.0882</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8006</v>
+        <v>5.6224</v>
       </c>
       <c r="F2" t="n">
         <v>-1.5342</v>
@@ -610,10 +610,10 @@
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0359</v>
+        <v>0.7859</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8468</v>
+        <v>-0.025</v>
       </c>
       <c r="U2" t="n">
         <v>0.8109</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2286</v>
+        <v>3.4988</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5333</v>
+        <v>2.9943</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6953</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>2.6565</v>
@@ -688,13 +688,13 @@
         <v>0.9702</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.116</v>
+        <v>0.1542</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3634</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2474</v>
+        <v>0.0567</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2821</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. REBERGEN</t>
+          <t>O. PEÑA LOPEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2495</v>
+        <v>0.2538</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2007</v>
+        <v>0.424</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4502</v>
+        <v>-0.1703</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1593</v>
+        <v>-2.2802</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5536</v>
+        <v>-2.6117</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3943</v>
+        <v>0.3314</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3936</v>
+        <v>-0.4708</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3707</v>
+        <v>-0.552</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0228</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2342</v>
+        <v>-1.8095</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1829</v>
+        <v>-2.0597</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4171</v>
+        <v>0.2502</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3576</v>
+        <v>0.5639</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1222</v>
+        <v>0.2829</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4798</v>
+        <v>0.281</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2239</v>
+        <v>0.6119</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2239</v>
+        <v>0.6119</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. PEÑA LOPEZ</t>
+          <t>J. RIES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2294</v>
+        <v>0.1309</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2634</v>
+        <v>-1.2299</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.034</v>
+        <v>1.3608</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2802</v>
+        <v>-0.7849</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.6117</v>
+        <v>-0.6286</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3314</v>
+        <v>-0.1563</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4708</v>
+        <v>-0.7886</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.552</v>
+        <v>0.4243</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08119999999999999</v>
+        <v>-1.2129</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8095</v>
+        <v>0.0037</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0597</v>
+        <v>-1.0529</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2502</v>
+        <v>1.0566</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
         <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5395</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1222</v>
+        <v>0.5288</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4172</v>
+        <v>-0.0011</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. RIES</t>
+          <t>I. REBERGEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0525</v>
+        <v>0.037</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0903</v>
+        <v>-0.4404</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1428</v>
+        <v>0.4774</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7849</v>
+        <v>0.1593</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6286</v>
+        <v>0.5536</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1563</v>
+        <v>-0.3943</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7886</v>
+        <v>0.3936</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4243</v>
+        <v>0.3707</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2129</v>
+        <v>0.0228</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0037</v>
+        <v>-0.2342</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0529</v>
+        <v>0.1829</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0566</v>
+        <v>-0.4171</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3881</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3582</v>
+        <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4493</v>
+        <v>-0.57</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6684</v>
+        <v>-0.1175</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2191</v>
+        <v>-0.4525</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>A. JIMENEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0499</v>
+        <v>-0.0775</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4101</v>
+        <v>0.1716</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3602</v>
+        <v>-0.2492</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6977</v>
+        <v>-0.202</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8922</v>
+        <v>-1.8554</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5899</v>
+        <v>1.6533</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1063</v>
+        <v>1.3409</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9845</v>
+        <v>0.0824</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1218</v>
+        <v>1.2585</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4087</v>
+        <v>-1.5429</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8768</v>
+        <v>-1.9378</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4681</v>
+        <v>0.3948</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.7164</v>
+        <v>-0.194</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5045</v>
+        <v>0.3185</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3963</v>
+        <v>-0.1991</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1081</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. JIMENEZ FERNANDEZ</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0257</v>
+        <v>-0.2144</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2507</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2764</v>
+        <v>-0.3057</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.202</v>
+        <v>0.6977</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8554</v>
+        <v>-0.8922</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6533</v>
+        <v>1.5899</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3409</v>
+        <v>1.1063</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0824</v>
+        <v>0.9845</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2585</v>
+        <v>0.1218</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5429</v>
+        <v>-0.4087</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9378</v>
+        <v>-1.8768</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3948</v>
+        <v>1.4681</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.194</v>
+        <v>-2.7164</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3703</v>
+        <v>1.2402</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.12</v>
+        <v>1.0775</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4904</v>
+        <v>0.1626</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7878</v>
+        <v>-1.979</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3534</v>
+        <v>0.0531</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1412</v>
+        <v>-2.0322</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4521</v>
@@ -1234,13 +1234,13 @@
         <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3643</v>
+        <v>0.173</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4251</v>
+        <v>0.1248</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0608</v>
+        <v>0.0482</v>
       </c>
       <c r="V10" t="n">
         <v>-0.894</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0589</v>
+        <v>-2.8982</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.45</v>
+        <v>-1.2893</v>
       </c>
       <c r="F11" t="n">
         <v>-1.6089</v>
@@ -1312,10 +1312,10 @@
         <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.157</v>
+        <v>0.0036</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3623</v>
+        <v>-0.2016</v>
       </c>
       <c r="U11" t="n">
         <v>0.2053</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1161</v>
+        <v>-4.425</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6871</v>
+        <v>-3.105</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4289</v>
+        <v>-1.3199</v>
       </c>
       <c r="G12" t="n">
         <v>-5.187</v>
@@ -1390,13 +1390,13 @@
         <v>1.9403</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2425</v>
+        <v>0.4486</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4229</v>
+        <v>0.1592</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1804</v>
+        <v>0.2894</v>
       </c>
       <c r="V12" t="n">
         <v>2.4477</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.5744</v>
+        <v>-6.9926</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3429</v>
+        <v>-5.5431</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2315</v>
+        <v>-1.4496</v>
       </c>
       <c r="G13" t="n">
         <v>-4.0911</v>
@@ -1468,13 +1468,13 @@
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3033</v>
+        <v>-0.115</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3623</v>
+        <v>-0.5625</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6656</v>
+        <v>0.4475</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8462</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.3105</v>
+        <v>-9.401900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.2201</v>
+        <v>-2.311600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.090300000000001</v>
+        <v>-7.0906</v>
       </c>
       <c r="G14" t="n">
         <v>-16.6072</v>
@@ -1516,16 +1516,16 @@
         <v>-13.8823</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.7251</v>
+        <v>-2.725100000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9333999999999989</v>
+        <v>0.9333999999999998</v>
       </c>
       <c r="K14" t="n">
         <v>0.7662000000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1670999999999999</v>
+        <v>0.1670999999999995</v>
       </c>
       <c r="M14" t="n">
         <v>-17.5407</v>
@@ -1546,10 +1546,10 @@
         <v>13.5823</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4282</v>
+        <v>3.3366</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1959</v>
+        <v>1.1045</v>
       </c>
       <c r="U14" t="n">
         <v>2.2321</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. VIDAL RODRIGUEZ</t>
+          <t>I. MENCARA JIMENEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9655</v>
+        <v>4.3879</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4651</v>
+        <v>2.3545</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4996</v>
+        <v>2.0333</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6155</v>
+        <v>4.1821</v>
       </c>
       <c r="H15" t="n">
-        <v>6.8529</v>
+        <v>1.7762</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2375</v>
+        <v>2.4058</v>
       </c>
       <c r="J15" t="n">
-        <v>6.4668</v>
+        <v>3.4991</v>
       </c>
       <c r="K15" t="n">
-        <v>6.4262</v>
+        <v>1.071</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0406</v>
+        <v>2.4281</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1487</v>
+        <v>0.6829</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4267</v>
+        <v>0.7052</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2781</v>
+        <v>-0.0223</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3582</v>
+        <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2126</v>
+        <v>-0.6763</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6539</v>
+        <v>-0.1744</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4413</v>
+        <v>-0.5019</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.8254</v>
+        <v>-0.2821</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3776</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4477</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>A. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6572</v>
+        <v>3.9839</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8593</v>
+        <v>4.5652</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7979000000000001</v>
+        <v>-0.5814</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6724</v>
+        <v>6.6155</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3345</v>
+        <v>6.8529</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3379</v>
+        <v>-0.2375</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6077</v>
+        <v>6.4668</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6591</v>
+        <v>6.4262</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9486</v>
+        <v>0.0406</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0646</v>
+        <v>0.1487</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3246</v>
+        <v>0.4267</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3893</v>
+        <v>-0.2781</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9702</v>
+        <v>0.3881</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9403</v>
+        <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8793</v>
+        <v>-0.1943</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8962</v>
+        <v>-0.5538</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0168</v>
+        <v>0.3595</v>
       </c>
       <c r="V16" t="n">
-        <v>0.894</v>
+        <v>-2.8254</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1179</v>
+        <v>-0.3776</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2239</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MENCARA JIMENEZ</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.542</v>
+        <v>3.8936</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7539</v>
+        <v>2.9594</v>
       </c>
       <c r="F17" t="n">
-        <v>1.788</v>
+        <v>0.9342</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1821</v>
+        <v>2.6724</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7762</v>
+        <v>0.3345</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4058</v>
+        <v>2.3379</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4991</v>
+        <v>2.6077</v>
       </c>
       <c r="K17" t="n">
-        <v>1.071</v>
+        <v>0.6591</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4281</v>
+        <v>1.9486</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6829</v>
+        <v>0.0646</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7052</v>
+        <v>-0.3246</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0223</v>
+        <v>0.3893</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5222</v>
+        <v>-0.6429</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.775</v>
+        <v>-0.7961</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7472</v>
+        <v>0.1531</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2821</v>
+        <v>0.894</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7818</v>
+        <v>1.8636</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.4758</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8572</v>
+        <v>2.3394</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3261</v>
@@ -1858,13 +1858,13 @@
         <v>2.3284</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8661</v>
+        <v>-0.0521</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4385</v>
+        <v>0.0381</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4276</v>
+        <v>-0.0902</v>
       </c>
       <c r="V18" t="n">
         <v>1.8836</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.096</v>
+        <v>1.2779</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0521</v>
+        <v>2.1522</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9560999999999999</v>
+        <v>-0.8744</v>
       </c>
       <c r="G19" t="n">
         <v>3.2379</v>
@@ -1936,13 +1936,13 @@
         <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3941</v>
+        <v>-0.2123</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2423</v>
+        <v>-0.1422</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1519</v>
+        <v>-0.0701</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5537</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.746</v>
+        <v>0.2812</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6378</v>
+        <v>-1.5387</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3838</v>
+        <v>1.8199</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8435</v>
@@ -2014,13 +2014,13 @@
         <v>2.5224</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4253</v>
+        <v>-0.0395</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1182</v>
+        <v>0.2173</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6929</v>
+        <v>-0.2568</v>
       </c>
       <c r="V20" t="n">
         <v>0.6119</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3663</v>
+        <v>-0.8297</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5753</v>
+        <v>-0.1749</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.791</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.3313</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8915999999999999</v>
+        <v>-0.355</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3511</v>
+        <v>0.0493</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5406</v>
+        <v>-0.4043</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2239</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5515</v>
+        <v>-1.5242</v>
       </c>
       <c r="E23" t="n">
         <v>-0.7121</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8393</v>
+        <v>-0.8121</v>
       </c>
       <c r="G23" t="n">
         <v>0.3514</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.0398</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3511</v>
       </c>
       <c r="U23" t="n">
-        <v>0.284</v>
+        <v>0.3113</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8358</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7543</v>
+        <v>-3.2177</v>
       </c>
       <c r="E24" t="n">
         <v>-2.0394</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7149</v>
+        <v>-1.1783</v>
       </c>
       <c r="G24" t="n">
         <v>1.3863</v>
@@ -2326,13 +2326,13 @@
         <v>2.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2474</v>
+        <v>-0.2159</v>
       </c>
       <c r="T24" t="n">
         <v>-0.5193</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7668</v>
+        <v>0.3034</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4477</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.3104</v>
+        <v>10.3105</v>
       </c>
       <c r="E25" t="n">
         <v>7.090400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>3.22</v>
+        <v>3.2199</v>
       </c>
       <c r="G25" t="n">
         <v>16.6073</v>
@@ -2386,13 +2386,13 @@
         <v>2.8922</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9335</v>
+        <v>-0.9335000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7664</v>
+        <v>-0.7663999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1672000000000001</v>
+        <v>-0.1672</v>
       </c>
       <c r="P25" t="n">
         <v>2.910600000000001</v>
@@ -2410,7 +2410,7 @@
         <v>-2.2322</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1960999999999998</v>
+        <v>-0.196</v>
       </c>
       <c r="V25" t="n">
         <v>-6.779100000000001</v>
